--- a/artfynd/A 19770-2025 artfynd.xlsx
+++ b/artfynd/A 19770-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125457403</v>
+        <v>125457999</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533599</v>
+        <v>533581</v>
       </c>
       <c r="R2" t="n">
-        <v>6885227</v>
+        <v>6885226</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125458094</v>
+        <v>125458612</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533824</v>
+        <v>533778</v>
       </c>
       <c r="R3" t="n">
-        <v>6885398</v>
+        <v>6885434</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125457873</v>
+        <v>125458094</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533692</v>
+        <v>533824</v>
       </c>
       <c r="R4" t="n">
-        <v>6885391</v>
+        <v>6885398</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125458212</v>
+        <v>125457649</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533826</v>
+        <v>533661</v>
       </c>
       <c r="R5" t="n">
-        <v>6885401</v>
+        <v>6885276</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125458675</v>
+        <v>125458212</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,19 +1129,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533700</v>
+        <v>533826</v>
       </c>
       <c r="R6" t="n">
-        <v>6885418</v>
+        <v>6885401</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125457915</v>
+        <v>125457634</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533712</v>
+        <v>533672</v>
       </c>
       <c r="R7" t="n">
-        <v>6885405</v>
+        <v>6885277</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125458297</v>
+        <v>125457915</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,39 +1323,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533841</v>
+        <v>533712</v>
       </c>
       <c r="R8" t="n">
-        <v>6885402</v>
+        <v>6885405</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125457756</v>
+        <v>125457873</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,7 +1452,7 @@
         <v>533692</v>
       </c>
       <c r="R9" t="n">
-        <v>6885357</v>
+        <v>6885391</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125458612</v>
+        <v>125458675</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,34 +1527,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533778</v>
+        <v>533700</v>
       </c>
       <c r="R10" t="n">
-        <v>6885434</v>
+        <v>6885418</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125457999</v>
+        <v>125458297</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,34 +1639,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533581</v>
+        <v>533841</v>
       </c>
       <c r="R11" t="n">
-        <v>6885226</v>
+        <v>6885402</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1704,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125457649</v>
+        <v>125457403</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533661</v>
+        <v>533599</v>
       </c>
       <c r="R12" t="n">
-        <v>6885276</v>
+        <v>6885227</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125457634</v>
+        <v>125457756</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533672</v>
+        <v>533692</v>
       </c>
       <c r="R13" t="n">
-        <v>6885277</v>
+        <v>6885357</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 19770-2025 artfynd.xlsx
+++ b/artfynd/A 19770-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125457999</v>
+        <v>125457915</v>
       </c>
       <c r="B2" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533581</v>
+        <v>533712</v>
       </c>
       <c r="R2" t="n">
-        <v>6885226</v>
+        <v>6885405</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125458612</v>
+        <v>125457873</v>
       </c>
       <c r="B3" t="n">
         <v>80028</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533778</v>
+        <v>533692</v>
       </c>
       <c r="R3" t="n">
-        <v>6885434</v>
+        <v>6885391</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125458094</v>
+        <v>125458612</v>
       </c>
       <c r="B4" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533824</v>
+        <v>533778</v>
       </c>
       <c r="R4" t="n">
-        <v>6885398</v>
+        <v>6885434</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125457649</v>
+        <v>125457403</v>
       </c>
       <c r="B5" t="n">
         <v>78947</v>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533661</v>
+        <v>533599</v>
       </c>
       <c r="R5" t="n">
-        <v>6885276</v>
+        <v>6885227</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125458212</v>
+        <v>125457634</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,39 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533826</v>
+        <v>533672</v>
       </c>
       <c r="R6" t="n">
-        <v>6885401</v>
+        <v>6885277</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125457634</v>
+        <v>125458094</v>
       </c>
       <c r="B7" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1201,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533672</v>
+        <v>533824</v>
       </c>
       <c r="R7" t="n">
-        <v>6885277</v>
+        <v>6885398</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125457915</v>
+        <v>125457999</v>
       </c>
       <c r="B8" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533712</v>
+        <v>533581</v>
       </c>
       <c r="R8" t="n">
-        <v>6885405</v>
+        <v>6885226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125457873</v>
+        <v>125458675</v>
       </c>
       <c r="B9" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,34 +1415,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533692</v>
+        <v>533700</v>
       </c>
       <c r="R9" t="n">
-        <v>6885391</v>
+        <v>6885418</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1480,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125458675</v>
+        <v>125458297</v>
       </c>
       <c r="B10" t="n">
         <v>57635</v>
@@ -1547,19 +1547,19 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533700</v>
+        <v>533841</v>
       </c>
       <c r="R10" t="n">
-        <v>6885418</v>
+        <v>6885402</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125458297</v>
+        <v>125458212</v>
       </c>
       <c r="B11" t="n">
         <v>57635</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533841</v>
+        <v>533826</v>
       </c>
       <c r="R11" t="n">
-        <v>6885402</v>
+        <v>6885401</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125457403</v>
+        <v>125457756</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533599</v>
+        <v>533692</v>
       </c>
       <c r="R12" t="n">
-        <v>6885227</v>
+        <v>6885357</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125457756</v>
+        <v>125457649</v>
       </c>
       <c r="B13" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533692</v>
+        <v>533661</v>
       </c>
       <c r="R13" t="n">
-        <v>6885357</v>
+        <v>6885276</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 19770-2025 artfynd.xlsx
+++ b/artfynd/A 19770-2025 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125457649</v>
+        <v>125458297</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1298,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533661</v>
+        <v>533841</v>
       </c>
       <c r="R8" t="n">
-        <v>6885276</v>
+        <v>6885402</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,6 +1363,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1384,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125458297</v>
+        <v>125457649</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,39 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533841</v>
+        <v>533661</v>
       </c>
       <c r="R9" t="n">
-        <v>6885402</v>
+        <v>6885276</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,11 +1465,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 19770-2025 artfynd.xlsx
+++ b/artfynd/A 19770-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>125458612</v>
       </c>
       <c r="B4" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125457634</v>
+        <v>125457915</v>
       </c>
       <c r="B5" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533672</v>
+        <v>533712</v>
       </c>
       <c r="R5" t="n">
-        <v>6885277</v>
+        <v>6885405</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125457915</v>
+        <v>125457634</v>
       </c>
       <c r="B6" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533712</v>
+        <v>533672</v>
       </c>
       <c r="R6" t="n">
-        <v>6885405</v>
+        <v>6885277</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125458297</v>
+        <v>125457649</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,39 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533841</v>
+        <v>533661</v>
       </c>
       <c r="R8" t="n">
-        <v>6885402</v>
+        <v>6885276</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,11 +1358,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125457649</v>
+        <v>125458297</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,34 +1395,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533661</v>
+        <v>533841</v>
       </c>
       <c r="R9" t="n">
-        <v>6885276</v>
+        <v>6885402</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,6 +1460,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,7 +1494,7 @@
         <v>125457999</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>125457403</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125457873</v>
+        <v>125457756</v>
       </c>
       <c r="B12" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>533692</v>
       </c>
       <c r="R12" t="n">
-        <v>6885391</v>
+        <v>6885357</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125457756</v>
+        <v>125457873</v>
       </c>
       <c r="B13" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>533692</v>
       </c>
       <c r="R13" t="n">
-        <v>6885357</v>
+        <v>6885391</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 19770-2025 artfynd.xlsx
+++ b/artfynd/A 19770-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>125458612</v>
       </c>
       <c r="B4" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125457915</v>
+        <v>125457634</v>
       </c>
       <c r="B5" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533712</v>
+        <v>533672</v>
       </c>
       <c r="R5" t="n">
-        <v>6885405</v>
+        <v>6885277</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125457634</v>
+        <v>125457915</v>
       </c>
       <c r="B6" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533672</v>
+        <v>533712</v>
       </c>
       <c r="R6" t="n">
-        <v>6885277</v>
+        <v>6885405</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
         <v>125457649</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>125457999</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>125457403</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125457756</v>
+        <v>125457873</v>
       </c>
       <c r="B12" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>533692</v>
       </c>
       <c r="R12" t="n">
-        <v>6885357</v>
+        <v>6885391</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125457873</v>
+        <v>125457756</v>
       </c>
       <c r="B13" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>533692</v>
       </c>
       <c r="R13" t="n">
-        <v>6885391</v>
+        <v>6885357</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 19770-2025 artfynd.xlsx
+++ b/artfynd/A 19770-2025 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125457649</v>
+        <v>125458297</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1298,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533661</v>
+        <v>533841</v>
       </c>
       <c r="R8" t="n">
-        <v>6885276</v>
+        <v>6885402</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,6 +1363,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1384,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125458297</v>
+        <v>125457649</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,39 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533841</v>
+        <v>533661</v>
       </c>
       <c r="R9" t="n">
-        <v>6885402</v>
+        <v>6885276</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,11 +1465,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 19770-2025 artfynd.xlsx
+++ b/artfynd/A 19770-2025 artfynd.xlsx
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125457634</v>
+        <v>125457915</v>
       </c>
       <c r="B5" t="n">
         <v>80075</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533672</v>
+        <v>533712</v>
       </c>
       <c r="R5" t="n">
-        <v>6885277</v>
+        <v>6885405</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125457915</v>
+        <v>125457634</v>
       </c>
       <c r="B6" t="n">
         <v>80075</v>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533712</v>
+        <v>533672</v>
       </c>
       <c r="R6" t="n">
-        <v>6885405</v>
+        <v>6885277</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125458297</v>
+        <v>125457649</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,39 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533841</v>
+        <v>533661</v>
       </c>
       <c r="R8" t="n">
-        <v>6885402</v>
+        <v>6885276</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,11 +1358,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125457649</v>
+        <v>125458297</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,34 +1395,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533661</v>
+        <v>533841</v>
       </c>
       <c r="R9" t="n">
-        <v>6885276</v>
+        <v>6885402</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,6 +1460,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1685,7 +1685,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125457873</v>
+        <v>125457756</v>
       </c>
       <c r="B12" t="n">
         <v>80075</v>
@@ -1723,7 +1723,7 @@
         <v>533692</v>
       </c>
       <c r="R12" t="n">
-        <v>6885391</v>
+        <v>6885357</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,7 +1782,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125457756</v>
+        <v>125457873</v>
       </c>
       <c r="B13" t="n">
         <v>80075</v>
@@ -1820,7 +1820,7 @@
         <v>533692</v>
       </c>
       <c r="R13" t="n">
-        <v>6885357</v>
+        <v>6885391</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 19770-2025 artfynd.xlsx
+++ b/artfynd/A 19770-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125458675</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125458130</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>125458612</v>
       </c>
       <c r="B4" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>125457915</v>
       </c>
       <c r="B5" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>125457634</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>125458212</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>125457649</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>125458297</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>125457999</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>125457403</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125457756</v>
+        <v>125457873</v>
       </c>
       <c r="B12" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>533692</v>
       </c>
       <c r="R12" t="n">
-        <v>6885357</v>
+        <v>6885391</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125457873</v>
+        <v>125457756</v>
       </c>
       <c r="B13" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>533692</v>
       </c>
       <c r="R13" t="n">
-        <v>6885391</v>
+        <v>6885357</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
